--- a/Memoria_Calculo_Hidraulica_Modelica.xlsx
+++ b/Memoria_Calculo_Hidraulica_Modelica.xlsx
@@ -19,7 +19,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pistola" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Boquilla" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pistola_cerrada" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuentes" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisiones_diseno" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuentes" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$4:$E$18</definedName>
@@ -58,9 +59,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Pistola_cerrada'!$A$4:$E$10</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="11">'Pistola_cerrada'!$1:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="11">'Pistola_cerrada'!$A$1:$E$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Fuentes'!$A$4:$E$11</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="12">'Fuentes'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="12">'Fuentes'!$A$1:$E$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="12" hidden="1">'Decisiones_diseno'!$A$4:$E$13</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="12">'Decisiones_diseno'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="12">'Decisiones_diseno'!$A$1:$E$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="13" hidden="1">'Fuentes'!$A$4:$E$11</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="13">'Fuentes'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="13">'Fuentes'!$A$1:$E$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -1782,6 +1786,318 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="27" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>DECISIONES DE DISEÑO BASADAS EN LA SIMULACIÓN</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Ciclo actual de 0–64 s · Evidencias e implicaciones de diseño · Resultados simulados, pendientes de calibración física</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Equipo / aspecto</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Decisión de diseño</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Resultado que la respalda</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Fuente / limitación</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Boquillas</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Usar alta de 1,15 mm en enjuague y baja de 4,6 mm al aplicar químicos.</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Alta: 100,827 bar(g) en entrada del Venturi a 9 s. Baja: 1,496 bar(g) en salida a 33 s.</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Decisión de diseño provisional</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>plant.gun.activeNozzleDiameter; plant.injectorInletPressure / OutletPressure. Confirmar diámetro de baja y Cd con la boquilla comercial.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="60" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Inyección downstream</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Conservar el inyector después de la hidrolavadora y aplicar químicos con baja contrapresión.</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Garganta en jabón: -0,304 bar(g); aspiración: 0,137 L/min.</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Respaldado por el modelo</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>plant.throatPressure y plant.injector.mChemical, t=33 s. General Pump 100819 es referencia comercial; los coeficientes hidráulicos siguen sin calibrar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="60" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Dosificación</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Mantener ajuste manual por aguja y calibrar cada producto por separado.</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Prelavado: 0,137; jabón: 0,137; cera: 0,074 L/min.</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Dosis estimadas, no garantizadas</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Instantáneas a 18, 33 y 48 s; no son promedios de etapa. Los químicos se representan como agua: confirmar viscosidad, densidad y concentración real.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="60" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Tanques y sifones</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Usar tapas con respiradero y conservar sifones de 12,7 mm interiores.</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Extracción desde tanque en jabón: 0,137 L/min; manifold: -0,279 bar(g).</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Configuración viable en el modelo</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Tanques atmosféricos y mangueras cebadas ideales. Longitud de 2 m y elevación de 0,5 m son supuestos; no se comparó esta ejecución con un tanque hermético.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="76" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Selección y purga</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Abrir una sola electroválvula y seleccionar baja presión durante la purga previa de 2 s.</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Apertura de la NC de jabón: 1; bloqueo de inyección: 0.</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Lógica comprobada en el ciclo</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>ProgramController y current-validation.json: máximo una rama abierta. La selección ideal representa el cambio de boquilla por el operador; 2 s no certifican limpieza ni eliminación de residuos químicos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Calentador externo</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Mantener entrada a 13 °C y ajuste manual de gas al máximo; usar temperatura con caudal para evaluar el servicio.</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Antes del cierre (55 s): 33,88 °C. Final sin flujo (64 s): 41,11 °C.</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Configuración térmica simulada</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>plant.inletHeater.T y m_flow. La temperatura a 64 s corresponde a agua retenida. Confirmar potencia útil del HACEB y compatibilidad térmica real de la TRENT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Protección de presión</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Clasificar componentes de alta presión por el máximo del circuito; no por la presión baja durante aplicación.</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Presión retenida con pistola cerrada (58 s): 116,98 bar(g); descarga: 0,000 L/min.</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Selección mecánica pendiente</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>plant.pumpOutletPressure. Límite parametrizado de bomba: 130 bar; añadir criterios físicos de transitorios y margen al seleccionar equipos. No se simularon golpes de ariete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="76" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Electroválvulas químicas</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Seleccionar NC aptas para aspiración y verificar aislamiento mediante checks.</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Jabón a 33 s: entrada NC -0,049; salida NC -0,068 bar(g).</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Especificación por confirmar</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Presiones normales de simulación, no ratings de compra. Compatibilidad de sellos, diferencial mínimo, vacío admisible y escenarios de fallo de checks deben confirmarse.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="76" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Validez del diseño</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Calibrar el prototipo antes de adoptar dosis y presiones como especificaciones finales.</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>La validación actual comprueba balances, exclusividad, aspiración y cierre.</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Validación del modelo, no del equipo</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>verification/results/current-validation.json. Los coeficientes de bomba, inyector, válvulas y Cd son supuestos. El límite de garganta puede actuar durante cambios de boquilla.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:E13"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
